--- a/data/trans_orig/P2B_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2B_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37440</t>
+          <t>37070</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51033</t>
+          <t>50580</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43980</t>
+          <t>44399</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59074</t>
+          <t>59544</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>85538</t>
+          <t>84348</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106094</t>
+          <t>106102</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,53%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27526</t>
+          <t>27979</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41119</t>
+          <t>41489</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29390</t>
+          <t>28920</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44484</t>
+          <t>44065</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>60929</t>
+          <t>60921</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81485</t>
+          <t>82675</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>49,5%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57961</t>
+          <t>58346</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79250</t>
+          <t>79311</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55145</t>
+          <t>54800</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75591</t>
+          <t>75796</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>120041</t>
+          <t>119472</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>149350</t>
+          <t>148354</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,46%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>107996</t>
+          <t>107935</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>129285</t>
+          <t>128900</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>113140</t>
+          <t>112935</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>133586</t>
+          <t>133931</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>226627</t>
+          <t>227623</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>255936</t>
+          <t>256505</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>68,22%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19944</t>
+          <t>18948</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33564</t>
+          <t>33039</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21677</t>
+          <t>21433</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36364</t>
+          <t>35590</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45266</t>
+          <t>44840</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65745</t>
+          <t>65438</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,49%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52915</t>
+          <t>53440</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66535</t>
+          <t>67531</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66897</t>
+          <t>67671</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81584</t>
+          <t>81828</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>123995</t>
+          <t>124302</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>144474</t>
+          <t>144900</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,37%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13023</t>
+          <t>14049</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27393</t>
+          <t>28014</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9387</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20738</t>
+          <t>20904</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26829</t>
+          <t>25991</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44382</t>
+          <t>44392</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>123682</t>
+          <t>123061</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>138052</t>
+          <t>137026</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>127356</t>
+          <t>127190</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>138707</t>
+          <t>138170</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>254787</t>
+          <t>254777</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>272340</t>
+          <t>273178</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,31%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>141510</t>
+          <t>143346</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>176257</t>
+          <t>175521</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>141508</t>
+          <t>145465</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>176911</t>
+          <t>180130</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>294665</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>343019</t>
+          <t>343331</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>327102</t>
+          <t>327838</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>361849</t>
+          <t>360013</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>351638</t>
+          <t>348419</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>387041</t>
+          <t>383084</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>688889</t>
+          <t>688577</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>737243</t>
+          <t>736872</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,41%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>96956</t>
+          <t>97406</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>103454</t>
+          <t>103464</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>104627</t>
+          <t>104245</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>110757</t>
+          <t>110766</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>204867</t>
+          <t>205169</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>213097</t>
+          <t>213317</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>657</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7416</t>
+          <t>7798</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>2846</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11296</t>
+          <t>10994</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>132146</t>
+          <t>132017</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>144949</t>
+          <t>145959</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>171468</t>
+          <t>170913</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>184107</t>
+          <t>184130</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>307703</t>
+          <t>307487</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>326137</t>
+          <t>326321</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14395</t>
+          <t>13385</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27198</t>
+          <t>27327</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>9094</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21756</t>
+          <t>22311</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26431</t>
+          <t>26247</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>44865</t>
+          <t>45081</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67969</t>
+          <t>67152</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82165</t>
+          <t>81459</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71000</t>
+          <t>71860</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84671</t>
+          <t>85911</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>144086</t>
+          <t>142097</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>162922</t>
+          <t>162553</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,36%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15815</t>
+          <t>16521</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30011</t>
+          <t>30828</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17141</t>
+          <t>15901</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30812</t>
+          <t>29952</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>36871</t>
+          <t>37240</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>55707</t>
+          <t>57696</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68361</t>
+          <t>69130</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86172</t>
+          <t>85326</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74860</t>
+          <t>75002</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92334</t>
+          <t>92935</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>150097</t>
+          <t>149051</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>173927</t>
+          <t>172974</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,15%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29348</t>
+          <t>30194</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47159</t>
+          <t>46390</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38737</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56211</t>
+          <t>56069</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>72664</t>
+          <t>73617</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>96494</t>
+          <t>97540</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,56%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>379315</t>
+          <t>380002</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>407294</t>
+          <t>407906</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>433225</t>
+          <t>436171</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>461879</t>
+          <t>462974</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>824703</t>
+          <t>822566</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>862665</t>
+          <t>861399</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,86%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69671</t>
+          <t>69059</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>97650</t>
+          <t>96963</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76272</t>
+          <t>75177</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>104926</t>
+          <t>101980</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>152450</t>
+          <t>153716</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>190412</t>
+          <t>192549</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85861</t>
+          <t>85781</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>95044</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>79088</t>
+          <t>79407</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90287</t>
+          <t>89718</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>167945</t>
+          <t>168466</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>182444</t>
+          <t>182458</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,87%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14474</t>
+          <t>14554</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>8549</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19179</t>
+          <t>18860</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16157</t>
+          <t>16143</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30656</t>
+          <t>30135</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>113335</t>
+          <t>114540</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>130504</t>
+          <t>129840</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>155909</t>
+          <t>154977</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>175317</t>
+          <t>174746</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>275617</t>
+          <t>275862</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>300318</t>
+          <t>300446</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,15%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23776</t>
+          <t>24440</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40945</t>
+          <t>39740</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31727</t>
+          <t>32298</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51135</t>
+          <t>52067</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>61006</t>
+          <t>60878</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>85707</t>
+          <t>85462</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79547</t>
+          <t>78300</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98109</t>
+          <t>97101</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75336</t>
+          <t>75880</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92841</t>
+          <t>92905</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>158707</t>
+          <t>160373</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>185397</t>
+          <t>184749</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,25%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44035</t>
+          <t>45043</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62597</t>
+          <t>63844</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35729</t>
+          <t>35665</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53234</t>
+          <t>52690</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85317</t>
+          <t>85965</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>112007</t>
+          <t>110341</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>40,76%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40622</t>
+          <t>39535</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59013</t>
+          <t>57896</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45430</t>
+          <t>47145</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65223</t>
+          <t>66972</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91956</t>
+          <t>91647</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>117298</t>
+          <t>117750</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,65%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60254</t>
+          <t>61371</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>78645</t>
+          <t>79732</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62628</t>
+          <t>60879</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82421</t>
+          <t>80706</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>129819</t>
+          <t>129367</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>155161</t>
+          <t>155470</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,91%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>332904</t>
+          <t>334612</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>368716</t>
+          <t>370677</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>372009</t>
+          <t>373103</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>409489</t>
+          <t>409824</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>717982</t>
+          <t>718387</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>767086</t>
+          <t>767403</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,2%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>147309</t>
+          <t>145348</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>183121</t>
+          <t>181413</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>152242</t>
+          <t>151907</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>189722</t>
+          <t>188628</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>310670</t>
+          <t>310353</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>359774</t>
+          <t>359369</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,34%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20187</t>
+          <t>19935</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31001</t>
+          <t>31257</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26991</t>
+          <t>26514</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38416</t>
+          <t>38862</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50646</t>
+          <t>49687</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66000</t>
+          <t>65896</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,85%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26130</t>
+          <t>25874</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36944</t>
+          <t>37196</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22450</t>
+          <t>22004</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33875</t>
+          <t>34352</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51997</t>
+          <t>52101</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67351</t>
+          <t>68310</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,89%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45390</t>
+          <t>47039</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64754</t>
+          <t>65794</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64145</t>
+          <t>63773</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85642</t>
+          <t>86662</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116164</t>
+          <t>115953</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143984</t>
+          <t>146279</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>43,26%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92918</t>
+          <t>91878</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>112282</t>
+          <t>110633</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>94834</t>
+          <t>93814</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>116331</t>
+          <t>116703</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>194164</t>
+          <t>191869</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>221984</t>
+          <t>222195</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,71%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47688</t>
+          <t>47730</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70490</t>
+          <t>69091</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49984</t>
+          <t>50818</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75049</t>
+          <t>75129</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>103871</t>
+          <t>105773</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>138124</t>
+          <t>139351</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>36,07%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>103398</t>
+          <t>104797</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>126200</t>
+          <t>126158</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137441</t>
+          <t>137361</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162506</t>
+          <t>161672</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>248254</t>
+          <t>247027</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>282507</t>
+          <t>280605</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>72,62%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45946</t>
+          <t>44220</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83141</t>
+          <t>83416</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75083</t>
+          <t>73455</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>120006</t>
+          <t>118793</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>129720</t>
+          <t>128032</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>186701</t>
+          <t>187687</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,34%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>191727</t>
+          <t>191452</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>228922</t>
+          <t>230648</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>185477</t>
+          <t>186690</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>230400</t>
+          <t>232028</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>393650</t>
+          <t>392664</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>450631</t>
+          <t>452319</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,94%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>174745</t>
+          <t>176846</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>229342</t>
+          <t>228486</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>236671</t>
+          <t>234238</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>291279</t>
+          <t>289888</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>428080</t>
+          <t>426337</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>505781</t>
+          <t>506888</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,62%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>434217</t>
+          <t>435073</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>488814</t>
+          <t>486713</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>468036</t>
+          <t>469427</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>522644</t>
+          <t>525077</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>917093</t>
+          <t>915986</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>994794</t>
+          <t>996537</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>70,04%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2B_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2B_R-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>51757</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>44400</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>58927</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>58,51%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>50,19%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>66,61%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>43890</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>37070</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>50580</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>37374</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>50696</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>55,87%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>47,19%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>64,39%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>51757</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>44399</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>59544</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>58,51%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>84348</t>
+          <t>84990</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106102</t>
+          <t>105672</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>63,27%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>36707</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>29537</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>44064</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>41,49%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>33,39%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>49,81%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>34669</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>27979</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>41489</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>27863</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>41185</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>44,13%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>35,61%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>52,81%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>36707</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>28920</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>44065</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>41,49%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>60921</t>
+          <t>61351</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>82675</t>
+          <t>82033</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,11%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>64941</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>55019</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>76061</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>34,41%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>29,15%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>40,3%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>69061</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>58346</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>79311</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>58308</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>79047</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>36,88%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>31,16%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>42,36%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>64941</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>54800</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>75796</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>34,41%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119472</t>
+          <t>119435</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>148354</t>
+          <t>149297</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,71%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>123790</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>112670</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>133712</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>65,59%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>59,7%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>70,85%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>118185</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>107935</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>128900</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>108199</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>128938</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>63,12%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>57,64%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>68,84%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>123790</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>112935</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>133931</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>65,59%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>227623</t>
+          <t>226680</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>256505</t>
+          <t>256542</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,23%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>28462</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>21787</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>36763</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>27,56%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>21,1%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35,6%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>26134</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18948</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>33039</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>19498</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>33578</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>30,22%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>38,2%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>28462</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>21433</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>35590</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>27,56%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44840</t>
+          <t>44720</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65438</t>
+          <t>65844</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,7%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>74799</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>66498</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>81474</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>72,44%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>64,4%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>78,9%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>60345</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>53440</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>67531</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>52901</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>66981</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>69,78%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>61,8%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>78,09%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>74799</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>67671</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>81828</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>72,44%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>124302</t>
+          <t>123896</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>144900</t>
+          <t>145020</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,43%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14879</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10078</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21428</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,05%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14,47%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>20011</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>14049</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>28014</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>13889</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>27714</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>13,25%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18,54%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>14879</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9924</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>20904</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25991</t>
+          <t>26155</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44392</t>
+          <t>43798</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>133215</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>126666</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>138016</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>89,95%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>85,53%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,2%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>131064</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>123061</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>137026</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>123361</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>137186</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>86,75%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>81,46%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>90,7%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>133215</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>127190</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>138170</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>89,95%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>254777</t>
+          <t>255371</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>273178</t>
+          <t>273014</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,26%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>160038</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>142875</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>177263</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>30,28%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>27,03%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>33,54%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>159096</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>143346</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>175521</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>141828</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>176193</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>31,61%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>28,48%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>34,87%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>160038</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>145465</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>180130</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>30,28%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>295036</t>
+          <t>293215</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>343331</t>
+          <t>342599</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>368511</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>351286</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>385674</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>69,72%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>66,46%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>72,97%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>507</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>344263</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>327838</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>360013</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>327166</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>361531</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>68,39%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>65,13%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>71,52%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>552</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>368511</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>348419</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>383084</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>69,72%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>688577</t>
+          <t>689309</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>736872</t>
+          <t>738693</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,59%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>108546</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>104607</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>110759</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>96,88%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>93,36%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>98,85%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>101458</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>97406</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>103464</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>97333</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>103416</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>97,44%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>93,55%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>108546</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>104245</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>110766</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>96,88%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>205169</t>
+          <t>204850</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>213317</t>
+          <t>213094</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3497</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7436</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>6,64%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>2663</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6715</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6788</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>2,56%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6,45%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>3497</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1277</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>7798</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2846</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10994</t>
+          <t>11313</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>112043</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>104121</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>112043</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>178384</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>171542</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>183811</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>92,32%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>88,78%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>95,13%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>139670</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>132017</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>145959</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>131921</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>146062</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>87,65%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>82,85%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>91,6%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>178384</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>170913</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>184130</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>92,32%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>307487</t>
+          <t>307478</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>326321</t>
+          <t>326269</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,54%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14840</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9413</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>21682</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4,87%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>11,22%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>19674</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>13385</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>27327</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>13282</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>27423</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>12,35%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,4%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>17,15%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>14840</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>9094</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>22311</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>7,68%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26247</t>
+          <t>26299</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45081</t>
+          <t>45090</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>78816</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>71618</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>84847</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>77,41%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>70,34%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>83,34%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>74941</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>67152</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>81459</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>67285</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>81300</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>76,49%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>68,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>83,14%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>78816</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>71860</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>85911</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>77,41%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>142097</t>
+          <t>142768</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>162553</t>
+          <t>162203</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,19%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>22996</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16965</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>30194</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>22,59%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>16,66%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>29,66%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>23039</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>16521</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>30828</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>16680</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>30695</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>23,51%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>16,86%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>31,46%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>22996</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>15901</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>29952</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>22,59%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37240</t>
+          <t>37590</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57696</t>
+          <t>57025</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>101812</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>101812</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>84054</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>75359</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>93633</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>64,13%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>57,49%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>71,44%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>77737</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>69130</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>85326</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>69964</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>85974</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>67,29%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>59,84%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>73,86%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>84054</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>75002</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>92935</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>64,13%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>149051</t>
+          <t>148855</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>172974</t>
+          <t>173924</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>70,53%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>47017</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>37438</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>55712</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>35,87%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>28,56%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>42,51%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>37783</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>30194</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>46390</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>29546</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>45556</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>32,71%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>26,14%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>40,16%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>47017</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>38136</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>56069</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>35,87%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>73617</t>
+          <t>72667</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>97540</t>
+          <t>97736</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,63%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>131071</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>131071</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>131071</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>115520</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>131071</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>131071</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>131071</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>449801</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>436342</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>464031</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>83,58%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>81,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>86,23%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>569</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>393806</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>380002</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>407906</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>379722</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>407139</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>82,57%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>79,67%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>85,52%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>449801</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>436171</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>462974</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>83,58%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>822566</t>
+          <t>824311</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>861399</t>
+          <t>862397</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,96%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>88350</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>74120</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>101809</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>16,42%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>13,77%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>18,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>83159</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>69059</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>96963</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>69826</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>97243</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>17,43%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>14,48%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>20,33%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>88350</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>75177</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>101980</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>16,42%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>153716</t>
+          <t>152718</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>192549</t>
+          <t>190804</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>538151</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>538151</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>538151</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>768</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>538151</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>538151</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>538151</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>85120</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>79283</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>90008</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>86,62%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>80,68%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>91,59%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>91045</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>85781</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>95044</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>85056</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>94856</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>90,74%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>85,49%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>94,73%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>85120</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>79407</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>89718</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>86,62%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>168466</t>
+          <t>169017</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>182458</t>
+          <t>182499</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,89%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13147</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8259</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>18984</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>13,38%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8,41%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>19,32%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>9290</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5291</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14554</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5479</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>15279</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>9,26%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>13147</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>8549</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>18860</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>13,38%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16143</t>
+          <t>16102</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30135</t>
+          <t>29584</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>100335</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>100335</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>100335</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>166151</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>155639</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>174910</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>80,25%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>75,17%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>84,48%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>194</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>122949</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>114540</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>129840</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>114869</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>130013</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>79,69%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>74,24%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>84,16%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>166151</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>154977</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>174746</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>80,25%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>275862</t>
+          <t>275454</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>300446</t>
+          <t>300896</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,28%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>40893</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>32134</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>51405</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>19,75%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>15,52%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>24,83%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>31331</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>24440</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>39740</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>24267</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>39411</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>20,31%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>15,84%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>25,76%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>40893</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>32298</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>52067</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>19,75%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>60878</t>
+          <t>60428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>85462</t>
+          <t>85870</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>207044</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>207044</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>207044</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>154280</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>154280</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>154280</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>207044</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>207044</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>207044</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>84693</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>75151</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>93713</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>65,87%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>58,45%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>72,89%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>88093</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>78300</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>97101</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>78553</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>97445</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>61,97%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>55,09%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>68,31%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>84693</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>75880</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>92905</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>65,87%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>160373</t>
+          <t>160154</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>184749</t>
+          <t>184756</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>43877</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>34857</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>53419</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>34,13%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>27,11%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>41,55%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>54051</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>45043</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>63844</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>44699</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>63591</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>38,03%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>31,69%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>44,91%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>43877</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>35665</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>52690</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>34,13%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85965</t>
+          <t>85958</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>110341</t>
+          <t>110560</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,84%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>128570</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>128570</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>128570</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>142144</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>142144</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>142144</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>128570</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>128570</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>128570</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,107 +5646,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>55709</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>46011</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>65230</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>43,57%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>35,99%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>51,02%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>48859</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>39535</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>57896</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>39969</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>59203</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>40,97%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>33,15%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>48,54%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>55709</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>47145</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>66972</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>43,57%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>33,51%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>49,64%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>104567</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>91123</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>117074</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>42,31%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>36,87%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>52,38%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>104567</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>91647</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>117750</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>42,31%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>37,09%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,38%</t>
         </is>
       </c>
     </row>
@@ -5759,107 +5759,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>72142</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>62621</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>81840</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>56,43%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>48,98%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>64,01%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>70408</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>61371</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>79732</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>60064</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>79298</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>59,03%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>51,46%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>66,85%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>72142</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>60879</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>80706</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>56,43%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>66,49%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>142550</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>130043</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>155994</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>57,69%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>52,62%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>63,13%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>142550</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>129367</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>155470</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>57,69%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>52,35%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>62,91%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>127851</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>127851</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>127851</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>119267</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>119267</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>119267</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>127851</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>127851</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>127851</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>391673</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>372627</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>408700</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>69,73%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>66,34%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>72,76%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>535</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>350945</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>334612</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>370677</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>333199</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>367020</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>68,01%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>64,84%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>71,83%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>571</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>391673</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>373103</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>409824</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>69,73%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>718387</t>
+          <t>719347</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>767403</t>
+          <t>766056</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,08%</t>
         </is>
       </c>
     </row>
@@ -6107,67 +6107,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>170058</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>153031</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>189104</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>30,27%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>27,24%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>33,66%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>165080</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>145348</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>181413</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>149005</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>182826</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>31,99%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>28,17%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>35,16%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>170058</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>151907</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>188628</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>30,27%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>310353</t>
+          <t>311700</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>359369</t>
+          <t>358409</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,26%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>812</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>561731</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>561731</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>561731</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>776</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>516025</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>516025</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>516025</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>812</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>561731</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>561731</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>561731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26842</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22065</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>31572</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>53,78%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>44,21%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>63,26%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>25385</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19935</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>31257</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>44,43%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>34,89%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>54,71%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>32886</t>
+          <t>22070</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26514</t>
+          <t>16957</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>27095</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>58271</t>
+          <t>48912</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49687</t>
+          <t>42344</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65896</t>
+          <t>56085</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,16%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>23069</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18339</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>27846</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>46,22%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>36,74%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>55,79%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>31746</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>25874</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>37196</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>55,57%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>45,29%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>65,11%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27980</t>
+          <t>29694</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22004</t>
+          <t>24669</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34352</t>
+          <t>34807</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>59726</t>
+          <t>52763</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52101</t>
+          <t>45590</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68310</t>
+          <t>59331</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>58,35%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>49911</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>49911</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>49911</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57131</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57131</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57131</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60866</t>
+          <t>51764</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>60866</t>
+          <t>51764</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60866</t>
+          <t>51764</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>117997</t>
+          <t>101675</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>117997</t>
+          <t>101675</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>117997</t>
+          <t>101675</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>65630</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>55808</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>76748</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>42,14%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>35,83%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>49,28%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>55124</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>47039</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>65794</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>34,96%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>29,83%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>41,73%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>74940</t>
+          <t>52774</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63773</t>
+          <t>44398</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86662</t>
+          <t>61850</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>130064</t>
+          <t>118403</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>115953</t>
+          <t>105500</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>146279</t>
+          <t>132818</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>44,28%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>90111</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>78993</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>99933</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>57,86%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>50,72%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>64,17%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>102548</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>91878</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>110633</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>65,04%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>58,27%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>70,17%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>105536</t>
+          <t>91462</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>93814</t>
+          <t>82386</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>116703</t>
+          <t>99838</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>208084</t>
+          <t>181574</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>191869</t>
+          <t>167159</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>222195</t>
+          <t>194477</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>64,83%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>155741</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>155741</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>155741</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>157672</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>157672</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>157672</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>180476</t>
+          <t>144236</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>180476</t>
+          <t>144236</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>180476</t>
+          <t>144236</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>338148</t>
+          <t>299977</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>338148</t>
+          <t>299977</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>338148</t>
+          <t>299977</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>63009</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>51458</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>75371</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>31,48%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>25,71%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>37,66%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>58675</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>47730</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>69091</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>33,74%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>27,45%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>39,73%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>62250</t>
+          <t>62693</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50818</t>
+          <t>51759</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75129</t>
+          <t>73581</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>120925</t>
+          <t>125702</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105773</t>
+          <t>108328</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>139351</t>
+          <t>141863</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>37,77%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>137117</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>124755</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>148668</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>68,52%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>62,34%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>74,29%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>115213</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>104797</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>126158</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>66,26%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>60,27%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>72,55%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>150240</t>
+          <t>112825</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137361</t>
+          <t>101937</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161672</t>
+          <t>123759</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>265453</t>
+          <t>249942</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>247027</t>
+          <t>233781</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>280605</t>
+          <t>267316</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>71,16%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>91773</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>74675</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>113707</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>31,36%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>25,52%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>38,85%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>65500</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>44220</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>83416</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>23,83%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>16,09%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>30,35%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>91058</t>
+          <t>64359</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73455</t>
+          <t>52200</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118793</t>
+          <t>76773</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>156558</t>
+          <t>156132</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>128032</t>
+          <t>134539</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>187687</t>
+          <t>182814</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>33,32%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>200872</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>178938</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>217970</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>68,64%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>61,15%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>74,48%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>209368</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>191452</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>230648</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>76,17%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>69,65%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>83,91%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>214425</t>
+          <t>191602</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>186690</t>
+          <t>179188</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>232028</t>
+          <t>203761</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>423793</t>
+          <t>392474</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>392664</t>
+          <t>365792</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>452319</t>
+          <t>414067</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>75,48%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>274868</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>274868</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>274868</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580351</t>
+          <t>548606</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580351</t>
+          <t>548606</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580351</t>
+          <t>548606</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>247254</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>223101</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>272696</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>35,4%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>31,94%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>39,04%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>305</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>204684</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>176846</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>228486</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>30,85%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>26,65%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>34,43%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>261135</t>
+          <t>201895</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>234238</t>
+          <t>181945</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>289888</t>
+          <t>221074</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>465819</t>
+          <t>449149</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>426337</t>
+          <t>416526</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>506888</t>
+          <t>483894</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>36,5%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>451169</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>425727</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>475322</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>64,6%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>60,96%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>68,06%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>634</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>458875</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>435073</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>486713</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>69,15%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>65,57%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>73,35%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>498180</t>
+          <t>425583</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>469427</t>
+          <t>406404</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>525077</t>
+          <t>445533</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>957055</t>
+          <t>876752</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>915986</t>
+          <t>842007</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>996537</t>
+          <t>909375</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>68,59%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>973</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>698423</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>698423</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>698423</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>939</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>663559</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>663559</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>663559</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>973</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>759315</t>
+          <t>627478</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>759315</t>
+          <t>627478</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>759315</t>
+          <t>627478</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1422874</t>
+          <t>1325901</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1422874</t>
+          <t>1325901</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1422874</t>
+          <t>1325901</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
